--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,414 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129849079</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98778</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvavasträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>816982</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7313026</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129849057</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98778</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvavasträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>817011</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7313045</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129849087</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvavasträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817010</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7313061</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129851096</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98778</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvavasträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>817060</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7313057</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hanna Gotlén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hanna Gotlén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>129851096</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,48 +989,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R5" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,52 +1094,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R6" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,52 +989,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R5" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1094,48 +1090,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R6" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,48 +989,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R5" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,52 +1094,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R6" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129851096</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129849087</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -989,52 +989,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R5" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1094,48 +1090,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R6" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129849087</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>129851096</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129851096</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,52 +989,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R5" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1094,48 +1090,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R6" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 733-2025 artfynd.xlsx
+++ b/artfynd/A 733-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129849079</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129849057</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,48 +989,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129849087</v>
+        <v>129851096</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvavasträsket, Nb</t>
+          <t>Kvavasträskberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817010</v>
+        <v>817060</v>
       </c>
       <c r="R5" t="n">
-        <v>7313061</v>
+        <v>7313057</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Hanna Gotlén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,52 +1094,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129851096</v>
+        <v>129849087</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvavasträskberget, Nb</t>
+          <t>Kvavasträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817060</v>
+        <v>817010</v>
       </c>
       <c r="R6" t="n">
-        <v>7313057</v>
+        <v>7313061</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Gotlén</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
